--- a/app/static/templates/excel/template_vocabulary.xlsx
+++ b/app/static/templates/excel/template_vocabulary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Vocabulary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vocabulary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/app/static/templates/excel/template_vocabulary.xlsx
+++ b/app/static/templates/excel/template_vocabulary.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -460,10 +460,13 @@
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="12" max="12"/>
+    <col width="45" customWidth="1" min="13" max="13"/>
+    <col width="31" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,20 +512,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>subcategory</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lesson_unit</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>image_url</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>collocations</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>antonyms</t>
         </is>
@@ -571,20 +589,35 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>CEFR</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>https://images.unsplash.com/photo-1434030216411-0b793f4b4173?w=500</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>accomplish a mission; accomplish a task</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>achieve, complete, fulfill</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>fail, abandon</t>
         </is>
@@ -633,20 +666,35 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
+          <t>CEFR</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Nature &amp; Climate</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
           <t>https://images.unsplash.com/photo-1542601906990-b4d3fb778b09?w=500</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>sustainable energy; sustainable development</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>eco-friendly, renewable</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>unsustainable, wasteful</t>
         </is>
@@ -693,18 +741,33 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>TOEIC</t>
+        </is>
+      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>Contracts &amp; Negotiations</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Part 7</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
           <t>negotiate a contract; negotiate terms</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>bargain, discuss</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>surrender</t>
         </is>
@@ -751,18 +814,33 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>IELTS</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
+          <t>Advanced Vocabulary</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Band 7.5+</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
           <t>pivotal role; pivotal moment</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>crucial, vital, critical</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>trivial, insignificant</t>
         </is>
